--- a/public/banner-ads/banners.xlsx
+++ b/public/banner-ads/banners.xlsx
@@ -1,44 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/public/banner-ads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F29804B-232C-4647-9842-018C0ED15179}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="banners" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>slot</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>alt</t>
+  </si>
+  <si>
+    <t>enabled</t>
+  </si>
+  <si>
+    <t>page</t>
+  </si>
+  <si>
+    <t>banner-1.png</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Banner quảng cáo 1</t>
+  </si>
+  <si>
+    <t>banner-2.png</t>
+  </si>
+  <si>
+    <t>Banner quảng cáo 2</t>
+  </si>
+  <si>
+    <t>banner-page-2-1.png</t>
+  </si>
+  <si>
+    <t>Banner quảng cáo 1 trang 2</t>
+  </si>
+  <si>
+    <t>banner-page-2-2.png</t>
+  </si>
+  <si>
+    <t>Banner quảng cáo 2 trang 2</t>
+  </si>
+  <si>
+    <t>https://sku02428.vercel.app/</t>
+  </si>
+  <si>
+    <t>https://sku-dino.vercel.app/</t>
+  </si>
+  <si>
+    <t>https://sku-resizer-02.vercel.app/</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -61,17 +114,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,41 +460,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>slot</v>
-      </c>
-      <c r="B1" t="str">
-        <v>image</v>
-      </c>
-      <c r="C1" t="str">
-        <v>url</v>
-      </c>
-      <c r="D1" t="str">
-        <v>alt</v>
-      </c>
-      <c r="E1" t="str">
-        <v>enabled</v>
-      </c>
-      <c r="F1" t="str">
-        <v>page</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>banner-1.png</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>Banner quảng cáo 1</v>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -439,18 +509,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>banner-2.png</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>Banner quảng cáo 2</v>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -459,18 +529,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="str">
-        <v>banner-page-2-1.png</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>Banner quảng cáo 1 trang 2</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -479,18 +549,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="str">
-        <v>banner-page-2-2.png</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>Banner quảng cáo 2 trang 2</v>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -500,8 +570,14 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{BECE5223-A0FC-6241-840C-98A3F0FDAA0F}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{2509CA91-98D2-894C-BF34-718361FA24EB}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{14E614CB-ECB2-3443-8F24-D0920E494D24}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError sqref="A1:F1 A5:F5 A2:B2 D2:F2 A3:B3 D3:F3 A4:B4 D4:F4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>